--- a/rules/swim_rules.xlsx
+++ b/rules/swim_rules.xlsx
@@ -1204,12 +1204,12 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>nose, ears, shoulders, hips</t>
+          <t>top_of_head, spine_at_neck, spine_at_waist</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Angle of ear→nose line relative to shoulder→hip line, non-breathing cycles</t>
+          <t>Angle of neck→top_of_head line relative to waist→neck spine line; positive = head raised. Median over the cycle</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1242,7 +1242,11 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>15-pt schema: replaces ear→nose vs shoulder→hip</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1272,12 +1276,12 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>nose, eyes, ears</t>
+          <t>top_of_head, spine_at_neck</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Vertical lift of head (ear midpoint) vs non-breathing baseline, normalized by head height</t>
+          <t>Rise of top_of_head (relative to neck) during the breath vs non-breathing frames, normalized by head height</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1310,7 +1314,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Should rotate, not lift</t>
+          <t>Should rotate, not lift. 15-pt schema: replaces ear midpoint</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1331,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>head_on</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1342,12 +1346,12 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>nose, wrists</t>
+          <t>top_of_head, spine_at_neck, wrists, shoulders</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Cycle fraction between same-side hand exit and peak head rotation</t>
+          <t>Cycle fraction between same-side hand exit (wrist rises above shoulder) and peak sideways head turn</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1380,7 +1384,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Late breath = head still turned as arm enters</t>
+          <t>Late breath = head still turned as arm enters. Moved side→head_on: head rotation is not visible from the side without face points</t>
         </is>
       </c>
     </row>

--- a/rules/swim_rules.xlsx
+++ b/rules/swim_rules.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>both</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>shoulder, elbow, wrist</t>
+          <t>shoulder, elbow, wrist (3D)</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Interior angle at elbow at mid-recovery (wrist passing shoulder)</t>
+          <t>True 3D interior elbow angle at mid-recovery (hand passing the shoulder), on the average stroke fused from side + head-on clips</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>Straighter recovery can be acceptable in open water; keep priority low</t>
+          <t>Straighter recovery can be acceptable in open water; keep priority low. Moved side→both: a side camera flattens the outward swing, so a good recovery read ~10° in 2D</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
   <autoFilter ref="A1:P19"/>
   <dataValidations count="6">
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$2:$A$3</formula1>
+      <formula1>=Lists!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$B$2:$B$4</formula1>
@@ -4772,6 +4772,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>either</t>

--- a/rules/swim_rules.xlsx
+++ b/rules/swim_rules.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,41 @@
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Parse with swim_rules.py: validates references and enums, scores metrics, ranks issues, exports JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Direct vs proxy evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Issue_Rules.evidence: 'direct' measures the fault itself; 'proxy' uses an indirect clue (e.g. where the hand breaks the surface, for a pull the deck camera cannot see).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Direct rule groups decide whenever they can be measured, even if a proxy disagrees. Proxy groups are used only when no direct group could be measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Issues.proxy_observed: required for any issue with a proxy rule. Shown instead of what_we_observed when the finding rests on a proxy; word it as 'may be ... would confirm it'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Proxy metrics have scored = no: they flag faults but never show the athlete a score.</t>
         </is>
       </c>
     </row>
@@ -655,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2003,6 +2038,402 @@
       <c r="P19" s="6" t="inlineStr">
         <is>
           <t>Informational only; no single ideal at self-selected pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>exit_reappear_position</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: where the hand breaks the surface</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>wrist, spine_at_waist (or hip)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>(wrist - low back) along direction of travel / torso, at the first frame the hand reappears after being hidden underwater; positive = past the hip</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips. Reads short of the true exit; over-gliders also read somewhat short</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>lead_hand_fraction</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: near hand out front</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>either</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>full_cycle</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>near wrist, top_of_head</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Share of the cycle the near hand is seen ahead of the head (unseen frames count as not ahead)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>cycle_frac</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>head_angle_horizontal</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: head angle above horizontal</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>full_cycle</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>top_of_head, spine_at_neck</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Angle of neck→top_of_head line above horizontal; needs no waist point</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips. Cannot separate a lifted head from a tilted body</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>head_height_head_on</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: head showing above shoulders</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>head_on</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>full_cycle</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>top_of_head, shoulders</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Height of top_of_head above the shoulder line / shoulder width, non-breathing frames</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips. Stands in for face visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>spine_angle</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: neck-to-low-back angle</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>either</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>full_cycle</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>spine_at_neck, spine_at_waist</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Angle of neck→low back line below horizontal; needs no ankles</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips. A lifted head also raises it</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>heel_rise</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Proxy: how high the heels come</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>either</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>kick</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>near ankle, spine_at_waist</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>95th percentile of (low back depth - ankle depth) / torso per cycle; positive = heel above the low back</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Proxy for deck footage; used only when no direct measurement of the issue was possible. Threshold calibrated on synthetic swimmers — verify on real clips. Sinking hips lower it</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2479,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2086,6 +2518,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>proxy_observed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -2179,6 +2616,11 @@
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Your hand may be leaving the water before it reaches your hip. We judged this from where your hand comes out of the water, because the pull itself wasn't visible. An underwater side view would confirm it.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2210,6 +2652,11 @@
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Your head may be lifted when you're not breathing. We judged this from your head angle alone, which can't fully tell a lifted head from a tilted body.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2400,6 +2847,11 @@
           <t>Often a consequence of head position; check that first</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Your hips may be riding low. We judged this from the line from your neck to your lower back, because your legs weren't clearly visible; an underwater side view would confirm it.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2431,6 +2883,11 @@
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Your knees may be bending a lot in the kick. We judged this from how high your heels come up; an underwater side view would confirm it.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2493,6 +2950,11 @@
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>You may be pausing with your arm out in front. We judged this from how long your hand stays ahead of your head; an underwater side view would confirm it.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2550,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2561,6 +3023,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2604,6 +3067,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -2630,6 +3098,11 @@
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2660,6 +3133,11 @@
           <t>Either condition triggers</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2686,6 +3164,11 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -2712,6 +3195,11 @@
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2738,6 +3226,11 @@
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2764,6 +3257,11 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2790,6 +3288,11 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2816,6 +3319,11 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2842,6 +3350,11 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2868,6 +3381,11 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2900,6 +3418,11 @@
           <t>Must occur in ≥50% of cycles</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2926,6 +3449,11 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2952,6 +3480,11 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2978,6 +3511,11 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3004,6 +3542,11 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -3030,6 +3573,11 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -3060,18 +3608,212 @@
           <t>AND with row above</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>short_pull</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>exit_reappear_position</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>over_gliding</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>lead_hand_fraction</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>high_head_position</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>head_angle_horizontal</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>high_head_position</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>head_height_head_on</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>sinking_hips</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>spine_angle</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>excessive_knee_bend</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>heel_rise</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H18"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lists!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Metrics!$A$2:$A$19</formula1>
+      <formula1>=Metrics!$A$2:$A$300</formula1>
     </dataValidation>
     <dataValidation sqref="A2:A300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Issues!$A$2:$A$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Lists!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4632,7 +5374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4686,6 +5428,11 @@
           <t>scored</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -4728,6 +5475,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -4768,6 +5520,11 @@
       <c r="H3" s="9" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>proxy</t>
         </is>
       </c>
     </row>

--- a/rules/swim_rules.xlsx
+++ b/rules/swim_rules.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>either</t>
+          <t>below</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1209,7 +1209,11 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Marked below: measuring it directly needs the hand seen through the pull/glide; from the deck it is only estimated by proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1923,7 +1927,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>either</t>
+          <t>below</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1971,7 +1975,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Some glide is fine for triathletes; flag only excessive dead spot</t>
+          <t>Some glide is fine for triathletes; flag only excessive dead spot Marked below: measuring it directly needs the hand seen through the pull/glide; from the deck it is only estimated by proxy.</t>
         </is>
       </c>
     </row>
